--- a/data/roster_nextgen.xlsx
+++ b/data/roster_nextgen.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/widmelu1/Documents/git/bbs-basel/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C708B82-1E30-C14E-8B2F-4F14348D084D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="20" yWindow="780" windowWidth="41120" windowHeight="24180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2020 Roster" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="2020 Roster" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,154 +25,145 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
-  <si>
-    <t xml:space="preserve">First</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Committee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Former</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antonella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazzei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lukas A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Widmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novartis Pharma AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muriel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F. Hoffmann-La Roche Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olympia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papachristofi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youyou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marques Barros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idorsia Pharmaceuticals Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mailing list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ottavia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prunas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University Hospital of Basel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manuela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zimmermann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rommers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celonic AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bechny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETH Zürich</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Committee</t>
+  </si>
+  <si>
+    <t>Former</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Antonella</t>
+  </si>
+  <si>
+    <t>Mazzei</t>
+  </si>
+  <si>
+    <t>BMS</t>
+  </si>
+  <si>
+    <t>Lukas A.</t>
+  </si>
+  <si>
+    <t>Widmer</t>
+  </si>
+  <si>
+    <t>Novartis Pharma AG</t>
+  </si>
+  <si>
+    <t>F. Hoffmann-La Roche Ltd</t>
+  </si>
+  <si>
+    <t>Olympia</t>
+  </si>
+  <si>
+    <t>Papachristofi</t>
+  </si>
+  <si>
+    <t>Youyou</t>
+  </si>
+  <si>
+    <t>Hu</t>
+  </si>
+  <si>
+    <t>Joana</t>
+  </si>
+  <si>
+    <t>Marques Barros</t>
+  </si>
+  <si>
+    <t>Idorsia Pharmaceuticals Ltd</t>
+  </si>
+  <si>
+    <t>Kristina</t>
+  </si>
+  <si>
+    <t>Weber</t>
+  </si>
+  <si>
+    <t>mailing list</t>
+  </si>
+  <si>
+    <t>Ottavia</t>
+  </si>
+  <si>
+    <t>Prunas</t>
+  </si>
+  <si>
+    <t>University Hospital of Basel</t>
+  </si>
+  <si>
+    <t>Manuela</t>
+  </si>
+  <si>
+    <t>Zimmermann</t>
+  </si>
+  <si>
+    <t>Nikki</t>
+  </si>
+  <si>
+    <t>Rommers</t>
+  </si>
+  <si>
+    <t>Michele</t>
+  </si>
+  <si>
+    <t>Firmo</t>
+  </si>
+  <si>
+    <t>Nicola</t>
+  </si>
+  <si>
+    <t>Nuti</t>
+  </si>
+  <si>
+    <t>Celonic AG</t>
+  </si>
+  <si>
+    <t>Michal</t>
+  </si>
+  <si>
+    <t>Bechny</t>
+  </si>
+  <si>
+    <t>ETH Zürich</t>
   </si>
   <si>
     <t xml:space="preserve">Ainesh </t>
   </si>
   <si>
-    <t xml:space="preserve">Sewak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Bern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robbie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peck</t>
+    <t>Sewak</t>
+  </si>
+  <si>
+    <t>University of Bern</t>
+  </si>
+  <si>
+    <t>Robbie</t>
+  </si>
+  <si>
+    <t>Peck</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,22 +172,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -208,7 +189,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -216,78 +197,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -346,60 +277,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -431,7 +378,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -455,7 +402,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -515,34 +462,33 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="101.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="101.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="6.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="9.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="8" style="2" width="101.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="1" width="101.51"/>
+    <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="2" customWidth="1"/>
+    <col min="8" max="20" width="101.5" style="2"/>
+    <col min="21" max="16384" width="101.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -575,12 +521,12 @@
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -591,27 +537,27 @@
         <v>12</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2">
         <v>1</v>
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -619,14 +565,14 @@
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -634,61 +580,61 @@
         <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -696,14 +642,14 @@
         <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2">
         <v>1</v>
       </c>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -711,14 +657,14 @@
         <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2">
         <v>1</v>
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -726,89 +672,75 @@
         <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" s="2">
         <v>1</v>
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2">
         <v>1</v>
       </c>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="3"/>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5001d4d2-76b9-44a6-bec6-5aee37463dca}" enabled="1" method="Privileged" siteId="{f35a6974-607f-47d4-82d7-ff31d7dc53a5}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/roster_nextgen.xlsx
+++ b/data/roster_nextgen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/widmelu1/Documents/git/bbs-basel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C708B82-1E30-C14E-8B2F-4F14348D084D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70657D8-3BAB-7F44-8EE3-BE22B7F6042F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="780" windowWidth="41120" windowHeight="24180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -612,7 +612,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
